--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\portfolio-alerts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\alerts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AC545C-921E-4EFD-94F1-D3C50823027B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FFB47-0003-433A-8114-068C8318A401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>symbol</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>LLOYDSENT</t>
+  </si>
+  <si>
+    <t>NSE</t>
+  </si>
+  <si>
+    <t>INDHOTEL</t>
   </si>
 </sst>
 </file>
@@ -434,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -504,7 +510,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -707,6 +713,20 @@
       </c>
       <c r="D19">
         <v>77.739999999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>721.01</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\alerts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FFB47-0003-433A-8114-068C8318A401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BC2C97-EC03-497B-89A4-2323EFF3210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -552,7 +552,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>100</v>
